--- a/output/pdf_financials_xlsx/DCOP.xlsx
+++ b/output/pdf_financials_xlsx/DCOP.xlsx
@@ -5170,43 +5170,43 @@
         <v>0.3862</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.3862</v>
+        <v>0.152017</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.579227</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.5319430000000001</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.360779</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.45844</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.270399</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.24797</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.038798</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.196385</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.196385</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.196385</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.161831</v>
       </c>
     </row>
     <row r="93">
@@ -8298,7 +8298,11 @@
           <t>Share‐based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -9256,7 +9260,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10340,7 +10348,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -11972,7 +11984,11 @@
           <t>Share-based payment reserve 279,077</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -13800,7 +13816,11 @@
           <t>Share-based payment reserve 270,399</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -15118,7 +15138,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -38041,10 +38065,10 @@
         </is>
       </c>
       <c r="L360" s="5" t="n">
-        <v>0.669555</v>
+        <v>-0.669555</v>
       </c>
       <c r="M360" s="5" t="n">
-        <v>11.255215</v>
+        <v>-11.255215</v>
       </c>
       <c r="N360" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DCOP.xlsx
+++ b/output/pdf_financials_xlsx/DCOP.xlsx
@@ -987,28 +987,28 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.011278</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.011349</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.006539</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.010181</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.001158</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001084</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001255</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000892</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000257</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.741356</v>
+        <v>-0.752634</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.743679</v>
+        <v>-0.755028</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.343963</v>
+        <v>-0.350502</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.960163</v>
+        <v>-0.970344</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.669555</v>
+        <v>-0.668471</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.669555</v>
+        <v>-0.6683</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.817477</v>
+        <v>-0.818369</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.817477</v>
@@ -1882,7 +1882,7 @@
         <v>-0.7419519999999999</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.82705</v>
+        <v>-0.827307</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-0.593282</v>
@@ -1958,16 +1958,16 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.741356</v>
+        <v>-0.752634</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.743679</v>
+        <v>-0.755028</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.343963</v>
+        <v>-0.350502</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.960163</v>
+        <v>-0.970344</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.669555</v>
+        <v>-0.668471</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.669555</v>
+        <v>-0.6683</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.817477</v>
+        <v>-0.818369</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.817477</v>
@@ -1990,7 +1990,7 @@
         <v>-0.7419519999999999</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.82705</v>
+        <v>-0.827307</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-0.593282</v>
@@ -2222,43 +2222,43 @@
         <v>0.000612</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.040168</v>
+        <v>0.036465</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.970396</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.020365</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.028518</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.290538</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.075656</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.373434</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.050184</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.174762</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.367554</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.322086</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.234098</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.113159</v>
       </c>
     </row>
     <row r="35">
@@ -2320,43 +2320,43 @@
         <v>1.307899</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.04323</v>
+        <v>1.039527</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.756051</v>
+        <v>2.726447</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.751165</v>
+        <v>0.77153</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.300345</v>
+        <v>0.328863</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.75136</v>
+        <v>1.041898</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.251115</v>
+        <v>0.326771</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.373434</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.050184</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.01575</v>
+        <v>0.190512</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.08</v>
+        <v>0.447554</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.0275</v>
+        <v>0.349586</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.234098</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.113159</v>
       </c>
     </row>
     <row r="37">
@@ -2911,40 +2911,40 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.211967</v>
+        <v>0.241571</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.496453</v>
+        <v>0.476088</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.494779</v>
+        <v>0.466261</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.573389</v>
+        <v>0.282851</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.42347</v>
+        <v>0.347814</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.373434</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.050184</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.5147620000000001</v>
+        <v>0.34</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.155736</v>
+        <v>0.788182</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.717541</v>
+        <v>0.395455</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.234098</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.315374</v>
+        <v>0.202215</v>
       </c>
     </row>
     <row r="49">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9754,7 +9754,11 @@
           <t>Reclamation Deposits (Note 5)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -10512,7 +10516,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -11296,7 +11300,11 @@
           <t>Reclamation Deposits (Note 6) 135,000</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -12488,7 +12496,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -13202,7 +13210,11 @@
           <t>Reclamation Deposits (Note 7) 135,000</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -14816,7 +14828,11 @@
           <t>Reclamation Deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -17538,7 +17554,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
@@ -18238,7 +18254,11 @@
           <t>Reclamation Deposits (Note 9)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E128" s="5" t="n">
         <v>0.110831</v>
       </c>
@@ -22874,7 +22894,11 @@
           <t>Recovery of reclamation deposit</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -23386,7 +23410,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -34370,7 +34398,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -36048,7 +36076,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -40874,7 +40902,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -42876,7 +42904,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -45184,7 +45212,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
